--- a/analysis_summary.xlsx
+++ b/analysis_summary.xlsx
@@ -56,7 +56,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="1"/>
@@ -1933,7 +1933,751 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">云南白药</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于云南白药 2025 年年报与年度审计意见（2026-04-01 披露）、2026 年一季报（公告日记为 2026-04-30，2026-04-29 晚间已进入公告系统）、2026-04-29 前复权收盘行情、东方财富近一年公告列表与质押公告正文</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发 Tier 1 一票否决，只有 1 个 Tier 2 黄灯。云南白药不是价值陷阱，但它当前的问题也不是“有没有雷”，而是“价格并不够低、现金转化也不够强”，因此只能进入观察池，不能按超低位逆向买入处理。</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">54.63元</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">53.50元</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">56.00元</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">59.80元</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1.21 : 1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">24% - 32%</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">6% - 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">伊利股份</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于伊利股份 2026-04-29 晚间披露、公告日为 2026-04-30 的 2026 年一季报与一季经营数据公告、2025 年年报及审计报告、2026-04-29 前复权收盘行情、2025-04-29 至 2026-04-29 公告检索</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发一票否决，但存在 2 个不能忽视的黄灯，即“短债滚动压力偏高”和“Q1 经营现金流覆盖仍未达到绿灯阈值”。伊利不是明显价值陷阱，但也不是可以无视赔率直接左侧抄底的标的。</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">26.57元</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">24.80元</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">28.20元</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">30.00元</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">0.92 : 1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">25% - 35%</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">10% - 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">公牛集团</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">可执行买入</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于公牛集团 2025 年年报与审计报告、2026 年一季报（东方财富公告列表与结构化财报字段已可检索，公告日期记为 2026-04-30）、2026-04-29 前复权日线、近一年公告标题检索</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发 Tier 1 一票否决，Tier 2 也维持绿灯。公牛集团当前不是“低位里的价值陷阱”，而是“正式财报已验证修复、但价格仍趴在两年低位”的可执行逆向标的。唯一需要持续盯防的是应收和存货增速是否会在中报继续快于收入。</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">41.34元</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">39.80元</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">45.20元</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">48.80元</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2.51 : 1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">8% - 14%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1% - 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">合盛硅业</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">暂时回避</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于 2025 年年报与审计报告（2026-04-16 披露）、已可检索的 2026 年一季报与 2026 年一季度主要经营数据公告（正文与 PDF 于 2026-04-29 晚间可检索，公告日字段记为 2026-04-30）、2026-04-29 前复权收盘行情、近一年公告标题检索与 2026-04-25 最新质押公告</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">严格按模板纪律，合盛硅业已经触发 Tier 1 的“流动性危机”一票否决项，当前裁决直接落在【暂时回避】。即便放松一票否决，它当前也不满足“超低位 + 高赔率”的逆向买入标准。</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">45.45元</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">42.80元</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">46.50元</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">50.50元</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">0.40 : 1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">46% - 54%</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">18% - 26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">同仁堂</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于同仁堂 2025 年年报与审计报告（2026-03-31 披露）、2026 年一季报（东方财富公告列表与结构化财报字段已可检索，公告日期记为 2026-04-30）、2026-04-29 前复权日线、近一年公告标题检索</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发一票否决，同仁堂不是财务安全问题，而是景气与估值匹配问题。Tier 2 已明确转为黄灯，因此必须要求至少 3 : 1 的保守盈亏比或等待右侧确认，不能仅凭极低分位直接开仓。</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">27.39元</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">26.80元</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">28.80元</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">31.10元</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2.39 : 1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">26% - 34%</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">8% - 14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">天坛生物</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于 2025 年年报与标准无保留审计意见（2026-03-28 披露）、2026 年一季报（公告日记为 2026-04-30，2026-04-29 晚间已可检索）、2026-04-29 前复权收盘行情、东方财富近一年公告列表与结构化财报字段、腾讯前复权日线</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发 Tier 1 一票否决，但 Tier 2 是实打实的黄灯。 天坛生物可以放进观察池，但不能仅凭“价格创两年新低”就直接归入当前可执行的超低位买入名单。</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">14.45元</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">13.70元</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">16.40元</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">18.00元</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2.60 : 1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">34% - 40%</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">12% - 18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">山西汾酒</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于东方财富已可检索的山西汾酒 2026 年第一季度报告正文与 2025 年年报（公告日期字段分别为 2026-04-30、2026-04-23）、2026-04-29 收盘行情与截至 2026-04-29 晚间可检索公开公告</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发一票否决。山西汾酒当前的核心矛盾不是财务安全，而是“景气降速下当前价位的赔率够不够高”。Tier 2 仍是黄灯，所以必须要求至少 3 : 1 的保守盈亏比，或者等待右侧确认，不能因为它是白酒里相对更优质的低位股就直接开仓。</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">143.14元</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">134.00元</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">154.40元</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">168.70元</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1.23 : 1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">32% - 40%</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">8% - 14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">星宇股份</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于星宇股份 2025 年年报与审计报告（2026-03-20 披露）、2026 年一季报（东方财富公告列表与结构化财报字段已于 2026-04-29 晚间可检索，公告日期记为 2026-04-30）、2026-04-29 前复权日线、近一年公告标题检索</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发 Tier 1 一票否决，Tier 2 也维持绿灯。星宇股份当前不是价值陷阱，唯一明确黄灯是 H 股发行上市带来的估值压制；但在当前位置，赔率还没有便宜到足以覆盖这一个黄灯，所以结论只能是观察等待，而不是直接执行买入。</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">125.70元</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">121.50元</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">133.50元</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">142.00元</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1.86 : 1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">16% - 22%</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3% - 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">春秋航空</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">可执行买入</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于 2025 年年报与财务报表及审计报告（2026-04-11 披露）、东方财富公告列表与结构化财报字段已可检索且公告日期记为 2026-04-30 的 2026 年一季报、2026-04-29 前复权收盘行情、近一年公告标题与控股股东质押公告正文</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发 Tier 1 一票否决，只有 1 个 Tier 1 黄灯，即“现金覆盖短债只是刚过线，短期偿债安全垫不厚”；Tier 2 则是明确绿灯。春秋航空当前不是价值陷阱，更接近“行业担忧仍在、但正式财报已经先修复”的低位修复票，因此允许进入可执行逆向买入池。</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">47.20元</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">45.70元</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">50.80元</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">53.50元</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2.40 : 1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">22% - 30%</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">4% - 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">片仔癀</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于 2025 年年报与 2026 年一季报（公告日期字段为 2026-04-30，2026-04-29 晚间已进入公告系统）、2026-04-29 前复权收盘行情、东方财富近一年公告列表与 2026Q1 主要经营数据公告正文</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发 Tier 1 一票否决，但 Tier 2 存在 1 个强黄灯。片仔癀当前不是价值陷阱型雷股，问题在于“增长放缓导致的估值重估还没走完，而当前位置的赔率也还不足以覆盖这个过程”，因此暂时只能放入观察池。</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">139.32元</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">135.80元</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">146.80元</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">155.50元</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2.13 : 1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">46% - 52%</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">12% - 18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">豪威集团</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于豪威集团 2025 年年报与审计报告相关公告（2026-03-31 披露）、2026 年一季报（公告日记为 2026-04-30，2026-04-29 晚间已进入公告系统）、2026-04-29 前复权日线、东方财富近一年公告标题与最新质押公告正文</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发 Tier 1 一票否决，但存在 2 个不能忽视的黄灯，即“控股股东高比例质押/H 股融资预期”与“利润斜率连续两个季度下修且库存偏快”。豪威集团不是典型价值陷阱，但它当前也不属于可以按超低位逻辑直接执行买入的标的。</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">101.59元</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">94.80元</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">107.20元</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">116.00元</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">0.83 : 1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">60% - 68%</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">22% - 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">重庆啤酒</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">观察等待</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Level A - 基于重庆啤酒 2025 年年报与 2025 年度财务审计报告（2026-03-11 披露）、2026 年一季报（公告日期记为 2026-04-30，2026-04-29 晚间已可检索）、2026-04-29 前复权收盘行情、东方财富近一年公告标题与嘉威诉讼进展公告正文</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">未触发 Tier 1 一票否决，但存在 2 个不能忽视的黄灯，即“高商誉包袱仍在”和“核心利润斜率仍偏弱”。重庆啤酒当前被否决的关键原因不是资产负债表会不会爆，而是它既不够便宜，也没有用明确的利润修复把商誉包袱重新定价。</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">56.19元</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">52.00元</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">60.00元</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">64.50元</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">0.91 : 1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">40% - 48%</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">14% - 20%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L30"/>
+  <autoFilter ref="A1:L42"/>
 </worksheet>
 </file>